--- a/testdata/lead/bulk_upload/priya_contact.xlsx
+++ b/testdata/lead/bulk_upload/priya_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Mani Varma</v>
+        <v>Avani Mehra</v>
       </c>
       <c r="B2" t="str">
-        <v>mani.varma612@gmail.com</v>
+        <v>avani.mehra830@gmail.com</v>
       </c>
       <c r="C2">
-        <v>7056519725</v>
+        <v>6356059340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Kannan Desai</v>
+        <v>Upendra Desai</v>
       </c>
       <c r="B3" t="str">
-        <v>kannan.desai878@gmail.com</v>
+        <v>upendra.desai782@gmail.com</v>
       </c>
       <c r="C3">
-        <v>9713714835</v>
+        <v>8798723350</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Chakravartee Namboothiri</v>
+        <v>Trilok Bhattacharya</v>
       </c>
       <c r="B4" t="str">
-        <v>chakravartee.namboothiri184@gmail.com</v>
+        <v>trilok.bhattacharya820@gmail.com</v>
       </c>
       <c r="C4">
-        <v>7030997057</v>
+        <v>9665808319</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Bishnu Patel</v>
+        <v>Shiv Nambeesan</v>
       </c>
       <c r="B5" t="str">
-        <v>bishnu.patel376@gmail.com</v>
+        <v>shiv.nambeesan380@gmail.com</v>
       </c>
       <c r="C5">
-        <v>8857303177</v>
+        <v>8778919029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sloka Pothuvaal</v>
+        <v>Menka Kaur</v>
       </c>
       <c r="B6" t="str">
-        <v>sloka.pothuvaal976@gmail.com</v>
+        <v>menka.kaur490@gmail.com</v>
       </c>
       <c r="C6">
-        <v>7916418227</v>
+        <v>7089623114</v>
       </c>
     </row>
   </sheetData>
